--- a/news/news-checker.xlsx
+++ b/news/news-checker.xlsx
@@ -480,7 +480,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -779,7 +778,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(placeholder screenshot)</t>
+          <t>straits-times-ai-models.png</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -794,7 +793,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Cover lead — still needs a real cover image</t>
+          <t>Image updated — Living Lab.png (941×1672, cropped 16:9)</t>
         </is>
       </c>
     </row>
